--- a/code/outputs/问题一/问题一_LP_求解结果_result1提交格式.xlsx
+++ b/code/outputs/问题一/问题一_LP_求解结果_result1提交格式.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="计划购电量" sheetId="1" r:id="Rde9550a574304688"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="充放电量" sheetId="2" r:id="R8872c743672c4235"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="计划购电量" sheetId="1" r:id="Rc0ad51767a534162"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="充放电量" sheetId="2" r:id="Rfc389991fc7045e1"/>
   </x:sheets>
 </x:workbook>
 </file>
